--- a/Result/profitability/5457.xlsx
+++ b/Result/profitability/5457.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-1.1</v>
       </c>
       <c r="M2" t="n">
-        <v>0.3412500000000001</v>
+        <v>0.11125</v>
       </c>
       <c r="N2" t="n">
-        <v>15.075</v>
+        <v>14.1025</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.52</v>
       </c>
       <c r="M3" t="n">
-        <v>0.09000000000000002</v>
+        <v>-0.02374999999999997</v>
       </c>
       <c r="N3" t="n">
-        <v>13.09125</v>
+        <v>13.04875</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,13 +899,13 @@
         <v>0.02</v>
       </c>
       <c r="M4" t="n">
-        <v>0.02250000000000002</v>
+        <v>-0.1575</v>
       </c>
       <c r="N4" t="n">
-        <v>12.5275</v>
+        <v>11.955</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-1.75</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.3325</v>
+        <v>-0.3</v>
       </c>
       <c r="N5" t="n">
-        <v>8.5525</v>
+        <v>8.1625</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.55</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.325</v>
+        <v>-0.50125</v>
       </c>
       <c r="N6" t="n">
-        <v>4.50625</v>
+        <v>3.96125</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.79</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.55625</v>
+        <v>-0.755</v>
       </c>
       <c r="N7" t="n">
-        <v>2.60625</v>
+        <v>1.965</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-0.35</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.755</v>
+        <v>-0.6737500000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>1.24125</v>
+        <v>1.2975</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1518,7 +1518,7 @@
         <v>-0.76</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.7250000000000001</v>
+        <v>-0.725</v>
       </c>
       <c r="N9" t="n">
         <v>-1.42</v>
@@ -1648,7 +1648,7 @@
         <v>-0.5975</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2362499999999998</v>
+        <v>-0.2362499999999996</v>
       </c>
       <c r="O10" t="n">
         <v>1</v>
@@ -1772,7 +1772,7 @@
         <v>0.25</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.5012500000000001</v>
+        <v>-0.50125</v>
       </c>
       <c r="N11" t="n">
         <v>1.6375</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>5457</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>5478</v>
+      </c>
+      <c r="D75" t="n">
+        <v>4740</v>
+      </c>
+      <c r="E75" t="n">
+        <v>738</v>
+      </c>
+      <c r="F75" t="n">
+        <v>13.47</v>
+      </c>
+      <c r="G75" t="n">
+        <v>69</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>1.25%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>45</v>
+      </c>
+      <c r="J75" t="n">
+        <v>114</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-69</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.4350000000000001</v>
+      </c>
+      <c r="N75" t="n">
+        <v>16.5775</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0.4500000000000011</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.03456221198156695</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.4262295081967213</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-3.119999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.1880650994575045</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
